--- a/logs/multihead_serial_grid/multihead_serial_grid.xlsx
+++ b/logs/multihead_serial_grid/multihead_serial_grid.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/multihead_serial_grid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00F58F44-2D2C-4624-AFBD-D09512EACA39}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5813804-54BB-4B81-9676-D6451415A310}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -5406,7 +5406,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C693527-CEE1-41DF-8F02-BE2C5DC86942}" name="Tabla1" displayName="Tabla1" ref="A1:BW55" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
-  <autoFilter ref="A1:BW55" xr:uid="{8C693527-CEE1-41DF-8F02-BE2C5DC86942}"/>
+  <autoFilter ref="A1:BW55" xr:uid="{8C693527-CEE1-41DF-8F02-BE2C5DC86942}">
+    <filterColumn colId="17">
+      <filters>
+        <filter val="3"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="75">
     <tableColumn id="1" xr3:uid="{0D75DC22-288D-4A8B-B551-2F7E6D92CB58}" name="date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{2968A711-44AD-48CE-BDD3-383F3656EA85}" name="model_id"/>
@@ -5981,7 +5987,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>46069.764999999999</v>
       </c>
@@ -6205,7 +6211,7 @@
         <v>-4.9288387756890373E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>46069.925370370373</v>
       </c>
@@ -6429,7 +6435,7 @@
         <v>-0.1137806995942503</v>
       </c>
     </row>
-    <row r="4" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>46070.080590277779</v>
       </c>
@@ -6653,7 +6659,7 @@
         <v>-0.24237459601996919</v>
       </c>
     </row>
-    <row r="5" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>46070.354120370372</v>
       </c>
@@ -6877,7 +6883,7 @@
         <v>-4.9402031019363253E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>46070.577847222223</v>
       </c>
@@ -7098,7 +7104,7 @@
         <v>-4.9288387756890373E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>46070.577893518523</v>
       </c>
@@ -7319,7 +7325,7 @@
         <v>-0.1137806995942503</v>
       </c>
     </row>
-    <row r="8" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>46070.577928240738</v>
       </c>
@@ -7540,7 +7546,7 @@
         <v>-0.24237459601996919</v>
       </c>
     </row>
-    <row r="9" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>46070.577951388892</v>
       </c>
@@ -7761,7 +7767,7 @@
         <v>-4.9402031019363253E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>46070.577997685177</v>
       </c>
@@ -7985,7 +7991,7 @@
         <v>-9.1470866287762576E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>46070.755844907413</v>
       </c>
@@ -8209,7 +8215,7 @@
         <v>-0.3243903143434268</v>
       </c>
     </row>
-    <row r="12" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>46070.89638888889</v>
       </c>
@@ -8433,7 +8439,7 @@
         <v>-0.12623117573152531</v>
       </c>
     </row>
-    <row r="13" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>46071.034537037027</v>
       </c>
@@ -8657,7 +8663,7 @@
         <v>-0.12636168955773969</v>
       </c>
     </row>
-    <row r="14" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>46071.176180555558</v>
       </c>
@@ -8881,7 +8887,7 @@
         <v>-0.21542206929366189</v>
       </c>
     </row>
-    <row r="15" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>46071.316435185188</v>
       </c>
@@ -10225,7 +10231,7 @@
         <v>-0.18568990984296671</v>
       </c>
     </row>
-    <row r="21" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>46072.722638888888</v>
       </c>
@@ -10449,7 +10455,7 @@
         <v>3.7884052647050299E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>46072.861145833333</v>
       </c>
@@ -10673,7 +10679,7 @@
         <v>-8.6962639228307381E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>46073.002152777779</v>
       </c>
@@ -10897,7 +10903,7 @@
         <v>-1.8873738491172579E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>46073.142418981479</v>
       </c>
@@ -11121,7 +11127,7 @@
         <v>-4.1611318189541668E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>46073.284363425933</v>
       </c>
@@ -11345,7 +11351,7 @@
         <v>-5.6476383580950085E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>46073.426006944443</v>
       </c>
@@ -11569,7 +11575,7 @@
         <v>7.4771514090120728E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>46073.603773148148</v>
       </c>
@@ -11793,7 +11799,7 @@
         <v>-5.2940711629155812E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>46073.776932870373</v>
       </c>
@@ -12017,7 +12023,7 @@
         <v>-0.1094067480443031</v>
       </c>
     </row>
-    <row r="29" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>46073.954513888893</v>
       </c>
@@ -12241,7 +12247,7 @@
         <v>2.409955739876446E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>46074.133090277777</v>
       </c>
@@ -12465,7 +12471,7 @@
         <v>1.386770465970844E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>46074.31622685185</v>
       </c>
@@ -12689,7 +12695,7 @@
         <v>-0.25475977294932672</v>
       </c>
     </row>
-    <row r="32" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>46074.465266203697</v>
       </c>
@@ -12913,7 +12919,7 @@
         <v>-0.36995586810986358</v>
       </c>
     </row>
-    <row r="33" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>46074.614340277767</v>
       </c>
@@ -13137,7 +13143,7 @@
         <v>-0.31338467687822941</v>
       </c>
     </row>
-    <row r="34" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>46074.750057870369</v>
       </c>
@@ -13361,7 +13367,7 @@
         <v>-0.19977513395151589</v>
       </c>
     </row>
-    <row r="35" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>46074.880115740743</v>
       </c>
@@ -13585,7 +13591,7 @@
         <v>-0.30116590462990328</v>
       </c>
     </row>
-    <row r="36" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>46075.001273148147</v>
       </c>
@@ -13809,7 +13815,7 @@
         <v>-5.5360478303240652E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>46075.141122685192</v>
       </c>
@@ -14033,7 +14039,7 @@
         <v>-0.1209109318080783</v>
       </c>
     </row>
-    <row r="38" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>46075.278124999997</v>
       </c>
@@ -14257,7 +14263,7 @@
         <v>-9.6756516030524597E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>46075.418194444443</v>
       </c>
@@ -14481,7 +14487,7 @@
         <v>-4.7799200805255022E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>46075.559236111112</v>
       </c>
@@ -14705,7 +14711,7 @@
         <v>-0.1147736823731491</v>
       </c>
     </row>
-    <row r="41" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>46075.700648148151</v>
       </c>
@@ -14929,7 +14935,7 @@
         <v>-0.7962959980963682</v>
       </c>
     </row>
-    <row r="42" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>46075.813298611109</v>
       </c>
@@ -15153,7 +15159,7 @@
         <v>-0.16562875484790471</v>
       </c>
     </row>
-    <row r="43" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>46075.926863425928</v>
       </c>
@@ -15377,7 +15383,7 @@
         <v>-0.67716301633327136</v>
       </c>
     </row>
-    <row r="44" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>46076.037824074083</v>
       </c>
@@ -15601,7 +15607,7 @@
         <v>-0.33837592540138178</v>
       </c>
     </row>
-    <row r="45" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>46076.148958333331</v>
       </c>
@@ -15825,7 +15831,7 @@
         <v>-0.29984060079710911</v>
       </c>
     </row>
-    <row r="46" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>46076.262511574067</v>
       </c>
@@ -16049,7 +16055,7 @@
         <v>-3.2601544279407202E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>46076.378171296303</v>
       </c>
@@ -16273,7 +16279,7 @@
         <v>-0.113303346273218</v>
       </c>
     </row>
-    <row r="48" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>46076.487500000003</v>
       </c>
@@ -16497,7 +16503,7 @@
         <v>-0.23692236332570141</v>
       </c>
     </row>
-    <row r="49" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>46076.654074074067</v>
       </c>
@@ -16721,7 +16727,7 @@
         <v>-0.56776905201915984</v>
       </c>
     </row>
-    <row r="50" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>46076.768703703703</v>
       </c>
@@ -18078,10 +18084,10 @@
   <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
